--- a/config/excel/CfgCombatEffects.xlsx
+++ b/config/excel/CfgCombatEffects.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatEffects" sheetId="1" r:id="Rdca84f9ff37c4c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatEffects" sheetId="1" r:id="R61cc9626f5164859"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+    <x:numFmt numFmtId="201" formatCode="0.###"/>
+    <x:numFmt numFmtId="202" formatCode="General"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -29,7 +34,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -51,6 +56,36 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -58,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -110,6 +145,39 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -336,10 +404,10 @@
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.25" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
@@ -347,185 +415,185 @@
     <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="16" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="19.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="20" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="20" t="str">
         <x:v>Kind</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="20" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="20" t="str">
         <x:v>DefinitionID</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="E1" s="20" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="20" t="str">
         <x:v>AttackCoefficient</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="G1" s="20" t="str">
         <x:v>CanCritical</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="20" t="str">
         <x:v>CanDodge</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="I1" s="20" t="str">
         <x:v>DurationTicks</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="J1" s="20" t="str">
         <x:v>LinkedID</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="K1" s="20" t="str">
         <x:v>Shape</x:v>
       </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="L1" s="20" t="str">
         <x:v>Radius</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="M1" s="20" t="str">
         <x:v>RadiusSource</x:v>
       </x:c>
-      <x:c r="N1" s="9" t="str">
+      <x:c r="N1" s="20" t="str">
         <x:v>Angle</x:v>
       </x:c>
-      <x:c r="O1" s="9" t="str">
+      <x:c r="O1" s="20" t="str">
         <x:v>Width</x:v>
       </x:c>
-      <x:c r="P1" s="9" t="str">
+      <x:c r="P1" s="20" t="str">
         <x:v>Height</x:v>
       </x:c>
-      <x:c r="Q1" s="9" t="str">
+      <x:c r="Q1" s="20" t="str">
         <x:v>RequireLineOfSight</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="10" t="str">
+      <x:c r="A2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="10" t="str">
+      <x:c r="B2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="str">
+      <x:c r="C2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="10" t="str">
+      <x:c r="D2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="10" t="str">
+      <x:c r="E2" s="21" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="F2" s="10" t="str">
+      <x:c r="F2" s="21" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="G2" s="10" t="str">
+      <x:c r="G2" s="21" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="H2" s="10" t="str">
+      <x:c r="H2" s="21" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="I2" s="10" t="str">
+      <x:c r="I2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="J2" s="10" t="str">
+      <x:c r="J2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="K2" s="10" t="str">
+      <x:c r="K2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="L2" s="10" t="str">
+      <x:c r="L2" s="21" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="M2" s="10" t="str">
+      <x:c r="M2" s="21" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="N2" s="10" t="str">
+      <x:c r="N2" s="21" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="O2" s="10" t="str">
+      <x:c r="O2" s="21" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="P2" s="10" t="str">
+      <x:c r="P2" s="21" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="Q2" s="10" t="str">
+      <x:c r="Q2" s="21" t="str">
         <x:v>bool</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="12" t="str">
+    <x:row r="3" ht="56" customHeight="1">
+      <x:c r="A3" s="22" t="str">
         <x:v># 效果配置编号。</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="22" t="str">
         <x:v>CombatEffectKind枚举值。</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="22" t="str">
         <x:v>CombatAttributeKind枚举值。</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="22" t="str">
         <x:v>事件与表现识别编号。</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="E3" s="22" t="str">
         <x:v>效果固定数值。</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F3" s="22" t="str">
         <x:v>来源攻击力倍率。</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="G3" s="22" t="str">
         <x:v>是否允许暴击。</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="H3" s="22" t="str">
         <x:v>是否允许闪避。</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="I3" s="22" t="str">
         <x:v>效果持续逻辑帧。</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="J3" s="22" t="str">
         <x:v>飞弹或Buff关联编号，其他类型填0。</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str">
+      <x:c r="K3" s="22" t="str">
         <x:v>CombatHitShape枚举值。</x:v>
       </x:c>
-      <x:c r="L3" s="12" t="str">
+      <x:c r="L3" s="22" t="str">
         <x:v>固定半径或装备范围附加值。</x:v>
       </x:c>
-      <x:c r="M3" s="12" t="str">
+      <x:c r="M3" s="22" t="str">
         <x:v>半径来源：0固定；1装备攻击范围加值。</x:v>
       </x:c>
-      <x:c r="N3" s="12" t="str">
+      <x:c r="N3" s="22" t="str">
         <x:v>扇形角度。</x:v>
       </x:c>
-      <x:c r="O3" s="12" t="str">
+      <x:c r="O3" s="22" t="str">
         <x:v>盒形宽度。</x:v>
       </x:c>
-      <x:c r="P3" s="12" t="str">
+      <x:c r="P3" s="22" t="str">
         <x:v>命中高度。</x:v>
       </x:c>
-      <x:c r="Q3" s="12" t="str">
+      <x:c r="Q3" s="22" t="str">
         <x:v>命中是否需要视线通畅。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="n">
+    <x:row r="4" ht="36" customHeight="1">
+      <x:c r="A4" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G4" s="7" t="b">
@@ -534,51 +602,51 @@
       <x:c r="H4" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="6" t="n">
+      <x:c r="I4" s="18" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O4" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P4" s="6" t="n">
+      <x:c r="J4" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q4" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="n">
+    <x:row r="5" ht="36" customHeight="1">
+      <x:c r="A5" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="23" t="n">
         <x:v>0.35</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="n">
+      <x:c r="F5" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="7" t="b">
@@ -587,51 +655,51 @@
       <x:c r="H5" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I5" s="6" t="n">
+      <x:c r="I5" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O5" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P5" s="6" t="n">
+      <x:c r="J5" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O5" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q5" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="6" t="n">
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="n">
+      <x:c r="B6" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="n">
+      <x:c r="E6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="7" t="b">
@@ -640,51 +708,51 @@
       <x:c r="H6" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O6" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6" s="6" t="n">
+      <x:c r="I6" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q6" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="6" t="n">
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="n">
+      <x:c r="B7" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="n">
+      <x:c r="E7" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="7" t="b">
@@ -693,51 +761,51 @@
       <x:c r="H7" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I7" s="6" t="n">
+      <x:c r="I7" s="18" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="J7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O7" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="6" t="n">
+      <x:c r="J7" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O7" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q7" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="6" t="n">
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="6" t="n">
+      <x:c r="B8" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="6" t="n">
+      <x:c r="E8" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="7" t="b">
@@ -746,51 +814,51 @@
       <x:c r="H8" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L8" s="6" t="n">
+      <x:c r="I8" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L8" s="23" t="n">
         <x:v>1.7</x:v>
       </x:c>
-      <x:c r="M8" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="6" t="n">
+      <x:c r="M8" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="23" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="O8" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="6" t="n">
+      <x:c r="O8" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="6" t="n">
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="n">
+      <x:c r="B9" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="n">
+      <x:c r="C9" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="6" t="n">
+      <x:c r="E9" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="7" t="b">
@@ -799,51 +867,51 @@
       <x:c r="H9" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O9" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P9" s="6" t="n">
+      <x:c r="I9" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O9" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="6" t="n">
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="6" t="n">
+      <x:c r="B10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="6" t="n">
+      <x:c r="E10" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G10" s="7" t="b">
@@ -852,51 +920,51 @@
       <x:c r="H10" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="6" t="n">
+      <x:c r="I10" s="18" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="J10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O10" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="6" t="n">
+      <x:c r="J10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O10" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="6" t="n">
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B11" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="n">
+      <x:c r="B11" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="n">
+      <x:c r="E11" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G11" s="7" t="b">
@@ -905,51 +973,51 @@
       <x:c r="H11" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O11" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11" s="6" t="n">
+      <x:c r="I11" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O11" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="6" t="n">
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B12" s="6" t="n">
+      <x:c r="B12" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="n">
+      <x:c r="C12" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="6" t="n">
+      <x:c r="E12" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G12" s="7" t="b">
@@ -958,51 +1026,51 @@
       <x:c r="H12" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O12" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="n">
+      <x:c r="I12" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O12" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="6" t="n">
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B13" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="n">
+      <x:c r="B13" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F13" s="6" t="n">
+      <x:c r="E13" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F13" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="7" t="b">
@@ -1011,51 +1079,51 @@
       <x:c r="H13" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O13" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P13" s="6" t="n">
+      <x:c r="I13" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O13" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q13" s="7" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="6" t="n">
+    <x:row r="14" ht="36" customHeight="1">
+      <x:c r="A14" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B14" s="6" t="n">
+      <x:c r="B14" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="6" t="n">
+      <x:c r="C14" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F14" s="6" t="n">
+      <x:c r="E14" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="7" t="b">
@@ -1064,32 +1132,562 @@
       <x:c r="H14" s="7" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M14" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="6" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O14" s="6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P14" s="6" t="n">
+      <x:c r="I14" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O14" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="b">
         <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" s="18" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E15" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G15" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="18" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O15" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q15" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="18" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E16" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="18" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O16" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q16" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="18" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E17" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="23" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="G17" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L17" s="23" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="M17" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="23" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O17" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P17" s="23" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="Q17" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="18" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="18" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q18" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" s="18" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E19" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="23" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="23" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M19" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O19" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q19" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" s="18" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E20" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" s="18" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O20" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q20" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" customHeight="1">
+      <x:c r="A21" s="18" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B21" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="23" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="M21" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O21" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q21" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" customHeight="1">
+      <x:c r="A22" s="18" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B22" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E22" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="18" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O22" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q22" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="36" customHeight="1">
+      <x:c r="A23" s="18" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B23" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E23" s="23" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F23" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" s="18" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L23" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N23" s="23" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O23" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P23" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q23" s="7" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="18" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B24" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E24" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="23" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="7" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L24" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M24" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N24" s="23" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O24" s="23" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="P24" s="23" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="Q24" s="7" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgCombatEffects.xlsx
+++ b/config/excel/CfgCombatEffects.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatEffects" sheetId="1" r:id="R61cc9626f5164859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatEffects" sheetId="1" r:id="R40e1219d8a544333"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -86,6 +86,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -93,7 +108,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -179,6 +194,31 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -418,176 +458,176 @@
     <x:col min="17" max="17" width="22.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="20" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="24" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="20" t="str">
+      <x:c r="B1" s="24" t="str">
         <x:v>Kind</x:v>
       </x:c>
-      <x:c r="C1" s="20" t="str">
+      <x:c r="C1" s="24" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="D1" s="20" t="str">
+      <x:c r="D1" s="24" t="str">
         <x:v>DefinitionID</x:v>
       </x:c>
-      <x:c r="E1" s="20" t="str">
+      <x:c r="E1" s="24" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="F1" s="20" t="str">
+      <x:c r="F1" s="24" t="str">
         <x:v>AttackCoefficient</x:v>
       </x:c>
-      <x:c r="G1" s="20" t="str">
+      <x:c r="G1" s="24" t="str">
         <x:v>CanCritical</x:v>
       </x:c>
-      <x:c r="H1" s="20" t="str">
+      <x:c r="H1" s="24" t="str">
         <x:v>CanDodge</x:v>
       </x:c>
-      <x:c r="I1" s="20" t="str">
+      <x:c r="I1" s="24" t="str">
         <x:v>DurationTicks</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
+      <x:c r="J1" s="24" t="str">
         <x:v>LinkedID</x:v>
       </x:c>
-      <x:c r="K1" s="20" t="str">
+      <x:c r="K1" s="24" t="str">
         <x:v>Shape</x:v>
       </x:c>
-      <x:c r="L1" s="20" t="str">
+      <x:c r="L1" s="24" t="str">
         <x:v>Radius</x:v>
       </x:c>
-      <x:c r="M1" s="20" t="str">
+      <x:c r="M1" s="24" t="str">
         <x:v>RadiusSource</x:v>
       </x:c>
-      <x:c r="N1" s="20" t="str">
+      <x:c r="N1" s="24" t="str">
         <x:v>Angle</x:v>
       </x:c>
-      <x:c r="O1" s="20" t="str">
+      <x:c r="O1" s="24" t="str">
         <x:v>Width</x:v>
       </x:c>
-      <x:c r="P1" s="20" t="str">
+      <x:c r="P1" s="24" t="str">
         <x:v>Height</x:v>
       </x:c>
-      <x:c r="Q1" s="20" t="str">
+      <x:c r="Q1" s="24" t="str">
         <x:v>RequireLineOfSight</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="21" t="str">
+      <x:c r="A2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B2" s="21" t="str">
+      <x:c r="B2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" s="21" t="str">
+      <x:c r="C2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D2" s="21" t="str">
+      <x:c r="D2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="21" t="str">
+      <x:c r="E2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="F2" s="21" t="str">
+      <x:c r="F2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="G2" s="21" t="str">
+      <x:c r="G2" s="25" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="H2" s="21" t="str">
+      <x:c r="H2" s="25" t="str">
         <x:v>bool</x:v>
       </x:c>
-      <x:c r="I2" s="21" t="str">
+      <x:c r="I2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="J2" s="21" t="str">
+      <x:c r="J2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="K2" s="21" t="str">
+      <x:c r="K2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="L2" s="21" t="str">
+      <x:c r="L2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="M2" s="21" t="str">
+      <x:c r="M2" s="25" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="N2" s="21" t="str">
+      <x:c r="N2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="O2" s="21" t="str">
+      <x:c r="O2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="P2" s="21" t="str">
+      <x:c r="P2" s="25" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="Q2" s="21" t="str">
+      <x:c r="Q2" s="25" t="str">
         <x:v>bool</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="56" customHeight="1">
-      <x:c r="A3" s="22" t="str">
+      <x:c r="A3" s="26" t="str">
         <x:v># 效果配置编号。</x:v>
       </x:c>
-      <x:c r="B3" s="22" t="str">
+      <x:c r="B3" s="26" t="str">
         <x:v>CombatEffectKind枚举值。</x:v>
       </x:c>
-      <x:c r="C3" s="22" t="str">
+      <x:c r="C3" s="26" t="str">
         <x:v>CombatAttributeKind枚举值。</x:v>
       </x:c>
-      <x:c r="D3" s="22" t="str">
+      <x:c r="D3" s="26" t="str">
         <x:v>事件与表现识别编号。</x:v>
       </x:c>
-      <x:c r="E3" s="22" t="str">
+      <x:c r="E3" s="26" t="str">
         <x:v>效果固定数值。</x:v>
       </x:c>
-      <x:c r="F3" s="22" t="str">
+      <x:c r="F3" s="26" t="str">
         <x:v>来源攻击力倍率。</x:v>
       </x:c>
-      <x:c r="G3" s="22" t="str">
+      <x:c r="G3" s="26" t="str">
         <x:v>是否允许暴击。</x:v>
       </x:c>
-      <x:c r="H3" s="22" t="str">
+      <x:c r="H3" s="26" t="str">
         <x:v>是否允许闪避。</x:v>
       </x:c>
-      <x:c r="I3" s="22" t="str">
+      <x:c r="I3" s="26" t="str">
         <x:v>效果持续逻辑帧。</x:v>
       </x:c>
-      <x:c r="J3" s="22" t="str">
+      <x:c r="J3" s="26" t="str">
         <x:v>飞弹或Buff关联编号，其他类型填0。</x:v>
       </x:c>
-      <x:c r="K3" s="22" t="str">
+      <x:c r="K3" s="26" t="str">
         <x:v>CombatHitShape枚举值。</x:v>
       </x:c>
-      <x:c r="L3" s="22" t="str">
+      <x:c r="L3" s="26" t="str">
         <x:v>固定半径或装备范围附加值。</x:v>
       </x:c>
-      <x:c r="M3" s="22" t="str">
+      <x:c r="M3" s="26" t="str">
         <x:v>半径来源：0固定；1装备攻击范围加值。</x:v>
       </x:c>
-      <x:c r="N3" s="22" t="str">
+      <x:c r="N3" s="26" t="str">
         <x:v>扇形角度。</x:v>
       </x:c>
-      <x:c r="O3" s="22" t="str">
+      <x:c r="O3" s="26" t="str">
         <x:v>盒形宽度。</x:v>
       </x:c>
-      <x:c r="P3" s="22" t="str">
+      <x:c r="P3" s="26" t="str">
         <x:v>命中高度。</x:v>
       </x:c>
-      <x:c r="Q3" s="22" t="str">
+      <x:c r="Q3" s="26" t="str">
         <x:v>命中是否需要视线通畅。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="36" customHeight="1">
-      <x:c r="A4" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C4" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="18" t="n">
+      <x:c r="A4" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="23" t="n">
@@ -596,25 +636,25 @@
       <x:c r="F4" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G4" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I4" s="18" t="n">
+      <x:c r="G4" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="23" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="J4" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K4" s="18" t="n">
+      <x:c r="J4" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L4" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M4" s="18" t="n">
+      <x:c r="M4" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N4" s="23" t="n">
@@ -626,21 +666,21 @@
       <x:c r="P4" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q4" s="7" t="b">
+      <x:c r="Q4" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
-      <x:c r="A5" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="18" t="n">
+      <x:c r="A5" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C5" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
@@ -649,25 +689,25 @@
       <x:c r="F5" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I5" s="18" t="n">
+      <x:c r="G5" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I5" s="23" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J5" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="18" t="n">
+      <x:c r="J5" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L5" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M5" s="18" t="n">
+      <x:c r="M5" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N5" s="23" t="n">
@@ -679,21 +719,21 @@
       <x:c r="P5" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q5" s="7" t="b">
+      <x:c r="Q5" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
-      <x:c r="A6" s="18" t="n">
+      <x:c r="A6" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="n">
+      <x:c r="B6" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
@@ -702,25 +742,25 @@
       <x:c r="F6" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G6" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I6" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="18" t="n">
+      <x:c r="G6" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H6" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L6" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="18" t="n">
+      <x:c r="M6" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N6" s="23" t="n">
@@ -732,21 +772,21 @@
       <x:c r="P6" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q6" s="7" t="b">
+      <x:c r="Q6" s="28" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
-      <x:c r="A7" s="18" t="n">
+      <x:c r="A7" s="23" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="n">
+      <x:c r="B7" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="23" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
@@ -755,25 +795,25 @@
       <x:c r="F7" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G7" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I7" s="18" t="n">
+      <x:c r="G7" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H7" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="23" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="J7" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
+      <x:c r="J7" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M7" s="18" t="n">
+      <x:c r="M7" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N7" s="23" t="n">
@@ -785,21 +825,21 @@
       <x:c r="P7" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q7" s="7" t="b">
+      <x:c r="Q7" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
-      <x:c r="A8" s="18" t="n">
+      <x:c r="A8" s="23" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="18" t="n">
+      <x:c r="B8" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="23" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
@@ -808,25 +848,25 @@
       <x:c r="F8" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G8" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I8" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="G8" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L8" s="23" t="n">
         <x:v>1.7</x:v>
       </x:c>
-      <x:c r="M8" s="18" t="n">
+      <x:c r="M8" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N8" s="23" t="n">
@@ -838,21 +878,21 @@
       <x:c r="P8" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q8" s="7" t="b">
+      <x:c r="Q8" s="28" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
-      <x:c r="A9" s="18" t="n">
+      <x:c r="A9" s="23" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="n">
+      <x:c r="B9" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="n">
+      <x:c r="C9" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="23" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
@@ -861,25 +901,25 @@
       <x:c r="F9" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G9" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I9" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="G9" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M9" s="18" t="n">
+      <x:c r="M9" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="23" t="n">
@@ -891,21 +931,21 @@
       <x:c r="P9" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q9" s="7" t="b">
+      <x:c r="Q9" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
-      <x:c r="A10" s="18" t="n">
+      <x:c r="A10" s="23" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B10" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="18" t="n">
+      <x:c r="B10" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
@@ -914,25 +954,25 @@
       <x:c r="F10" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I10" s="18" t="n">
+      <x:c r="G10" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="23" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="J10" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="J10" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="18" t="n">
+      <x:c r="M10" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N10" s="23" t="n">
@@ -944,21 +984,21 @@
       <x:c r="P10" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q10" s="7" t="b">
+      <x:c r="Q10" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
-      <x:c r="A11" s="18" t="n">
+      <x:c r="A11" s="23" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B11" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="n">
+      <x:c r="B11" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="23" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
@@ -967,25 +1007,25 @@
       <x:c r="F11" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G11" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I11" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="G11" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L11" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="18" t="n">
+      <x:c r="M11" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N11" s="23" t="n">
@@ -997,21 +1037,21 @@
       <x:c r="P11" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q11" s="7" t="b">
+      <x:c r="Q11" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
-      <x:c r="A12" s="18" t="n">
+      <x:c r="A12" s="23" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B12" s="18" t="n">
+      <x:c r="B12" s="23" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="n">
+      <x:c r="C12" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="n">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
@@ -1020,25 +1060,25 @@
       <x:c r="F12" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I12" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="G12" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L12" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="18" t="n">
+      <x:c r="M12" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N12" s="23" t="n">
@@ -1050,21 +1090,21 @@
       <x:c r="P12" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q12" s="7" t="b">
+      <x:c r="Q12" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
-      <x:c r="A13" s="18" t="n">
+      <x:c r="A13" s="23" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B13" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="18" t="n">
+      <x:c r="B13" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
@@ -1073,25 +1113,25 @@
       <x:c r="F13" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="7" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="7" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="G13" s="28" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="28" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="18" t="n">
+      <x:c r="M13" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N13" s="23" t="n">
@@ -1103,21 +1143,21 @@
       <x:c r="P13" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q13" s="7" t="b">
+      <x:c r="Q13" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
-      <x:c r="A14" s="18" t="n">
+      <x:c r="A14" s="23" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B14" s="18" t="n">
+      <x:c r="B14" s="23" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="n">
+      <x:c r="C14" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="23" t="n">
@@ -1126,25 +1166,25 @@
       <x:c r="F14" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="G14" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L14" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="18" t="n">
+      <x:c r="M14" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="23" t="n">
@@ -1156,21 +1196,21 @@
       <x:c r="P14" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q14" s="7" t="b">
+      <x:c r="Q14" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
-      <x:c r="A15" s="18" t="n">
+      <x:c r="A15" s="23" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B15" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="n">
+      <x:c r="B15" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="23" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="23" t="n">
@@ -1179,25 +1219,25 @@
       <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G15" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I15" s="18" t="n">
+      <x:c r="G15" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="23" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="J15" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="J15" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L15" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="18" t="n">
+      <x:c r="M15" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N15" s="23" t="n">
@@ -1209,21 +1249,21 @@
       <x:c r="P15" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q15" s="7" t="b">
+      <x:c r="Q15" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
-      <x:c r="A16" s="18" t="n">
+      <x:c r="A16" s="23" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B16" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="n">
+      <x:c r="B16" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="23" t="n">
         <x:v>41</x:v>
       </x:c>
       <x:c r="E16" s="23" t="n">
@@ -1232,25 +1272,25 @@
       <x:c r="F16" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I16" s="18" t="n">
+      <x:c r="G16" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="23" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J16" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="J16" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L16" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="18" t="n">
+      <x:c r="M16" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N16" s="23" t="n">
@@ -1262,21 +1302,21 @@
       <x:c r="P16" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q16" s="7" t="b">
+      <x:c r="Q16" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
-      <x:c r="A17" s="18" t="n">
+      <x:c r="A17" s="23" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B17" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="18" t="n">
+      <x:c r="B17" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="n">
         <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="23" t="n">
@@ -1285,25 +1325,25 @@
       <x:c r="F17" s="23" t="n">
         <x:v>1.15</x:v>
       </x:c>
-      <x:c r="G17" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I17" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="G17" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L17" s="23" t="n">
         <x:v>1.8</x:v>
       </x:c>
-      <x:c r="M17" s="18" t="n">
+      <x:c r="M17" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N17" s="23" t="n">
@@ -1315,21 +1355,21 @@
       <x:c r="P17" s="23" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="Q17" s="7" t="b">
+      <x:c r="Q17" s="28" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="36" customHeight="1">
-      <x:c r="A18" s="18" t="n">
+      <x:c r="A18" s="23" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B18" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="n">
+      <x:c r="B18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E18" s="23" t="n">
@@ -1338,25 +1378,25 @@
       <x:c r="F18" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G18" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I18" s="18" t="n">
+      <x:c r="G18" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="23" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="J18" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="J18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L18" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="18" t="n">
+      <x:c r="M18" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N18" s="23" t="n">
@@ -1368,21 +1408,21 @@
       <x:c r="P18" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q18" s="7" t="b">
+      <x:c r="Q18" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="36" customHeight="1">
-      <x:c r="A19" s="18" t="n">
+      <x:c r="A19" s="23" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B19" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="18" t="n">
+      <x:c r="B19" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="n">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="23" t="n">
@@ -1391,25 +1431,25 @@
       <x:c r="F19" s="23" t="n">
         <x:v>1.4</x:v>
       </x:c>
-      <x:c r="G19" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I19" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="G19" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L19" s="23" t="n">
         <x:v>3.2</x:v>
       </x:c>
-      <x:c r="M19" s="18" t="n">
+      <x:c r="M19" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N19" s="23" t="n">
@@ -1421,21 +1461,21 @@
       <x:c r="P19" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q19" s="7" t="b">
+      <x:c r="Q19" s="28" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="36" customHeight="1">
-      <x:c r="A20" s="18" t="n">
+      <x:c r="A20" s="23" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B20" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="18" t="n">
+      <x:c r="B20" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="23" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E20" s="23" t="n">
@@ -1444,25 +1484,25 @@
       <x:c r="F20" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G20" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I20" s="18" t="n">
+      <x:c r="G20" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" s="23" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="J20" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="J20" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L20" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="18" t="n">
+      <x:c r="M20" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N20" s="23" t="n">
@@ -1474,21 +1514,21 @@
       <x:c r="P20" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q20" s="7" t="b">
+      <x:c r="Q20" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="36" customHeight="1">
-      <x:c r="A21" s="18" t="n">
+      <x:c r="A21" s="23" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B21" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="18" t="n">
+      <x:c r="B21" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="n">
         <x:v>61</x:v>
       </x:c>
       <x:c r="E21" s="23" t="n">
@@ -1497,25 +1537,25 @@
       <x:c r="F21" s="23" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="G21" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I21" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="G21" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="23" t="n">
         <x:v>3.2</x:v>
       </x:c>
-      <x:c r="M21" s="18" t="n">
+      <x:c r="M21" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N21" s="23" t="n">
@@ -1527,21 +1567,21 @@
       <x:c r="P21" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q21" s="7" t="b">
+      <x:c r="Q21" s="28" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="36" customHeight="1">
-      <x:c r="A22" s="18" t="n">
+      <x:c r="A22" s="23" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B22" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="n">
+      <x:c r="B22" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="23" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E22" s="23" t="n">
@@ -1550,25 +1590,25 @@
       <x:c r="F22" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G22" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I22" s="18" t="n">
+      <x:c r="G22" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="23" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="J22" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="J22" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L22" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="18" t="n">
+      <x:c r="M22" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N22" s="23" t="n">
@@ -1580,21 +1620,21 @@
       <x:c r="P22" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q22" s="7" t="b">
+      <x:c r="Q22" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="36" customHeight="1">
-      <x:c r="A23" s="18" t="n">
+      <x:c r="A23" s="23" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B23" s="18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="n">
+      <x:c r="B23" s="23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="23" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="E23" s="23" t="n">
@@ -1603,25 +1643,25 @@
       <x:c r="F23" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I23" s="18" t="n">
+      <x:c r="G23" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" s="23" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J23" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="J23" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L23" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="18" t="n">
+      <x:c r="M23" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N23" s="23" t="n">
@@ -1633,21 +1673,21 @@
       <x:c r="P23" s="23" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q23" s="7" t="b">
+      <x:c r="Q23" s="28" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
-      <x:c r="A24" s="18" t="n">
+      <x:c r="A24" s="23" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B24" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C24" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="18" t="n">
+      <x:c r="B24" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="E24" s="23" t="n">
@@ -1656,25 +1696,25 @@
       <x:c r="F24" s="23" t="n">
         <x:v>1.25</x:v>
       </x:c>
-      <x:c r="G24" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="7" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I24" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J24" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="G24" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" s="23" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L24" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M24" s="18" t="n">
+      <x:c r="M24" s="23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N24" s="23" t="n">
@@ -1686,8 +1726,220 @@
       <x:c r="P24" s="23" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="Q24" s="7" t="b">
-        <x:v>1</x:v>
+      <x:c r="Q24" s="28" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="27" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="B25" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="27" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="E25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="27" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="K25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N25" s="27" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P25" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q25" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="27" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="B26" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="27" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="E26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="27" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G26" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N26" s="27" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P26" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q26" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="27" t="n">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="B27" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="27" t="n">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="E27" s="27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N27" s="27" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P27" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q27" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="27" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="B28" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="27" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="E28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="27" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="G28" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="29" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N28" s="27" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O28" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P28" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q28" s="29" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/excel/CfgCombatEffects.xlsx
+++ b/config/excel/CfgCombatEffects.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatEffects" sheetId="1" r:id="R40e1219d8a544333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgCombatEffects" sheetId="1" r:id="R0c4b188d20964940"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1942,6 +1942,218 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q29" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" customHeight="1">
+      <x:c r="A30" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L30" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N30" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="O30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q30" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" customHeight="1">
+      <x:c r="A31" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N31" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q31" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="36" customHeight="1">
+      <x:c r="A32" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H32" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L32" t="n">
+        <x:v>3.7</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N32" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q32" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
